--- a/data/analysis_gemini_2_5_flash_qwen2_audio/multimodal_event_eval_gemini_2_5_flash_qwen2_audio_w1_0s_h0_5s.xlsx
+++ b/data/analysis_gemini_2_5_flash_qwen2_audio/multimodal_event_eval_gemini_2_5_flash_qwen2_audio_w1_0s_h0_5s.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="50">
   <si>
     <t>event</t>
   </si>
@@ -112,19 +112,19 @@
     <t>sound: shout(0-156), sound: shout(204-240), sound: gunshot_or_explosion(48-72), sound: impact(108-216), visual: carrying(168-240), visual: physical_altercation(48-48)</t>
   </si>
   <si>
-    <t>sound: impact(0-36), sound: impact(60-96), sound: impact(120-216), sound: shout(24-72), sound: shout(216-240), sound: gunshot_or_explosion(84-132), sound: gunshot_or_explosion(168-228), visual: enter_or_exit_vehicle(0-0), visual: explosion_visible(120-216), visual: explosion_visible(120-240), visual: gunshot_visible(48-96), visual: physical_altercation(48-96), visual: running(144-168), visual: running(144-168), visual: suspicious_near_vehicle(72-96), visual: suspicious_near_vehicle(96-96), visual: vehicle_collision(216-216), visual: vehicle_collision(216-216), visual: vehicle_collision(216-216)</t>
-  </si>
-  <si>
-    <t>sound: impact(0-60), sound: impact(192-240), sound: shout(24-48), sound: shout(72-192), sound: gunshot_or_explosion(48-84), sound: horn(180-204)</t>
-  </si>
-  <si>
-    <t>sound: shout(0-24), sound: shout(48-240), sound: impact(12-60), sound: gunshot_or_explosion(108-144), sound: gunshot_or_explosion(192-216), visual: carrying(168-240), visual: enter_or_exit_vehicle(240-240), visual: running(168-168), visual: suspicious_near_vehicle(192-192), visual: suspicious_near_vehicle(168-240)</t>
+    <t>sound: impact(0-216), sound: shout(24-72), sound: shout(216-240), sound: gunshot_or_explosion(84-132), sound: gunshot_or_explosion(168-228), visual: enter_or_exit_vehicle(0-0), visual: explosion_visible(120-216), visual: explosion_visible(120-240), visual: gunshot_visible(48-96), visual: physical_altercation(48-96), visual: running(144-168), visual: running(144-168), visual: suspicious_near_vehicle(72-96), visual: suspicious_near_vehicle(96-96), visual: vehicle_collision(216-216), visual: vehicle_collision(216-216), visual: vehicle_collision(216-216)</t>
+  </si>
+  <si>
+    <t>sound: impact(0-60), sound: impact(192-240), sound: shout(24-192), sound: gunshot_or_explosion(48-84), sound: horn(180-204)</t>
+  </si>
+  <si>
+    <t>sound: shout(0-240), sound: impact(12-60), sound: gunshot_or_explosion(108-144), sound: gunshot_or_explosion(192-216), visual: carrying(168-240), visual: enter_or_exit_vehicle(240-240), visual: running(168-168), visual: suspicious_near_vehicle(192-192), visual: suspicious_near_vehicle(168-240)</t>
   </si>
   <si>
     <t>sound: gunshot_or_explosion(0-36), sound: impact(24-60), sound: impact(120-144), sound: impact(180-204), sound: engine(48-96), sound: engine(168-228), sound: shout(84-240), visual: explosion_visible(24-72), visual: explosion_visible(48-48), visual: explosion_visible(72-240), visual: running(24-48), visual: running(168-192), visual: running(168-240), visual: running(168-240)</t>
   </si>
   <si>
-    <t>sound: engine(0-24), sound: impact(12-108), sound: impact(132-156), sound: gunshot_or_explosion(24-48), sound: gunshot_or_explosion(120-144), sound: shout(96-240), visual: explosion_visible(192-240), visual: vehicle_collision(192-240)</t>
+    <t>sound: engine(0-24), sound: impact(12-156), sound: gunshot_or_explosion(24-48), sound: gunshot_or_explosion(120-144), sound: shout(96-240), visual: explosion_visible(192-240), visual: vehicle_collision(192-240)</t>
   </si>
   <si>
     <t>NO</t>
@@ -136,16 +136,16 @@
     <t>sound: shout(0-84), sound: impact(72-96), sound: impact(216-240), sound: engine(84-228), sound: tire_squeal(180-216), visual: enter_or_exit_vehicle(72-168), visual: running(24-24), visual: suspicious_near_vehicle(48-48)</t>
   </si>
   <si>
-    <t>sound: shout(0-72), sound: shout(96-132), sound: shout(192-216), sound: impact(36-108), sound: impact(144-168), sound: impact(204-240), sound: engine(72-96), sound: engine(120-204), visual: enter_or_exit_vehicle(24-96), visual: running(24-24), visual: suspicious_near_vehicle(24-24), visual: suspicious_near_vehicle(96-240)</t>
-  </si>
-  <si>
-    <t>sound: horn(0-48), sound: shout(36-84), sound: shout(156-180), sound: shout(204-240), sound: impact(72-216), sound: engine(84-120), sound: gunshot_or_explosion(120-144)</t>
+    <t>sound: shout(0-132), sound: shout(192-216), sound: impact(36-108), sound: impact(144-168), sound: impact(204-240), sound: engine(72-204), visual: enter_or_exit_vehicle(24-96), visual: running(24-24), visual: suspicious_near_vehicle(24-24), visual: suspicious_near_vehicle(96-240)</t>
+  </si>
+  <si>
+    <t>sound: horn(0-48), sound: shout(36-84), sound: shout(156-240), sound: impact(72-216), sound: engine(84-120), sound: gunshot_or_explosion(120-144)</t>
   </si>
   <si>
     <t>sound: engine(0-24), sound: impact(12-108), sound: impact(204-240), sound: tire_squeal(24-48), sound: shout(36-60), sound: shout(120-216), sound: gunshot_or_explosion(96-132)</t>
   </si>
   <si>
-    <t>sound: engine(0-24), sound: horn(12-60), sound: shout(48-84), sound: shout(108-168), sound: impact(72-240), visual: enter_or_exit_vehicle(120-120), visual: enter_or_exit_vehicle(144-240), visual: suspicious_near_vehicle(144-240), visual: vehicle_collision(72-240), visual: vehicle_collision(72-240)</t>
+    <t>sound: engine(0-24), sound: horn(12-60), sound: shout(48-168), sound: impact(72-240), visual: enter_or_exit_vehicle(120-120), visual: enter_or_exit_vehicle(144-240), visual: suspicious_near_vehicle(144-240), visual: vehicle_collision(72-240), visual: vehicle_collision(72-240)</t>
   </si>
   <si>
     <t>visual: enter_or_exit_vehicle(48-168), visual: suspicious_near_vehicle(48-192)</t>
@@ -166,13 +166,13 @@
     <t>visual: carrying(168-168), visual: suspicious_near_vehicle(216-240), visual: suspicious_near_vehicle(216-216), visual: suspicious_near_vehicle(240-240), visual: suspicious_near_vehicle(216-216)</t>
   </si>
   <si>
-    <t>sound: shout(0-228), sound: impact(132-156), sound: impact(180-240), visual: physical_altercation(0-144)</t>
-  </si>
-  <si>
-    <t>sound: shout(0-216), sound: gunshot_or_explosion(120-144), sound: impact(156-180), sound: impact(204-240), visual: physical_altercation(0-120), visual: running(24-72), visual: running(24-72)</t>
-  </si>
-  <si>
-    <t>sound: impact(0-144), sound: impact(180-228), sound: shout(12-48), sound: shout(144-192), sound: shout(216-240), sound: gunshot_or_explosion(108-132), sound: tire_squeal(132-156), visual: enter_or_exit_vehicle(48-240), visual: running(0-24), visual: suspicious_near_vehicle(48-72)</t>
+    <t>sound: shout(0-228), sound: impact(132-240), visual: physical_altercation(0-144)</t>
+  </si>
+  <si>
+    <t>sound: shout(0-216), sound: gunshot_or_explosion(120-144), sound: impact(156-240), visual: physical_altercation(0-120), visual: running(24-72), visual: running(24-72)</t>
+  </si>
+  <si>
+    <t>sound: impact(0-144), sound: impact(180-228), sound: shout(12-48), sound: shout(144-240), sound: gunshot_or_explosion(108-132), sound: tire_squeal(132-156), visual: enter_or_exit_vehicle(48-240), visual: running(0-24), visual: suspicious_near_vehicle(48-72)</t>
   </si>
   <si>
     <t>sound: impact(0-24), sound: impact(72-144), sound: impact(192-240), sound: shout(12-192), sound: engine(180-204), visual: enter_or_exit_vehicle(48-240), visual: running(0-24), visual: suspicious_near_vehicle(48-48)</t>
@@ -181,7 +181,7 @@
     <t>sound: engine(0-24), sound: horn(12-72), sound: impact(60-240), sound: gunshot_or_explosion(84-120), sound: shout(120-144), visual: enter_or_exit_vehicle(216-216), visual: suspicious_near_vehicle(216-216), visual: suspicious_near_vehicle(216-216), visual: vehicle_collision(72-120), visual: vehicle_collision(96-240), visual: vehicle_collision(72-240)</t>
   </si>
   <si>
-    <t>sound: tire_squeal(0-24), sound: shout(12-48), sound: shout(84-132), sound: shout(156-216), sound: gunshot_or_explosion(36-60), sound: impact(48-96), sound: impact(120-240)</t>
+    <t>sound: tire_squeal(0-24), sound: shout(12-48), sound: shout(84-216), sound: gunshot_or_explosion(36-60), sound: impact(48-240)</t>
   </si>
   <si>
     <t>visual: enter_or_exit_vehicle(48-168), visual: running(216-240), visual: suspicious_near_vehicle(48-96), visual: suspicious_near_vehicle(168-192)</t>
@@ -585,19 +585,19 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>0.625</v>
+        <v>0.714</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>0.769</v>
+        <v>0.833</v>
       </c>
       <c r="E2">
         <v>5</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1654,7 +1654,7 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1696,7 +1696,7 @@
         <v>34</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
@@ -1705,23 +1705,6 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>34</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" t="s">
         <v>45</v>
       </c>
     </row>

--- a/data/analysis_gemini_2_5_flash_qwen2_audio/multimodal_event_eval_gemini_2_5_flash_qwen2_audio_w1_0s_h0_5s.xlsx
+++ b/data/analysis_gemini_2_5_flash_qwen2_audio/multimodal_event_eval_gemini_2_5_flash_qwen2_audio_w1_0s_h0_5s.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="51">
   <si>
     <t>event</t>
   </si>
@@ -137,6 +137,9 @@
   </si>
   <si>
     <t>sound: shout(0-132), sound: shout(192-216), sound: impact(36-108), sound: impact(144-168), sound: impact(204-240), sound: engine(72-204), visual: enter_or_exit_vehicle(24-96), visual: running(24-24), visual: suspicious_near_vehicle(24-24), visual: suspicious_near_vehicle(96-240)</t>
+  </si>
+  <si>
+    <t>visual: enter_or_exit_vehicle(24-96), visual: running(24-24), visual: suspicious_near_vehicle(24-24), visual: suspicious_near_vehicle(96-240)</t>
   </si>
   <si>
     <t>sound: horn(0-48), sound: shout(36-84), sound: shout(156-240), sound: impact(72-216), sound: engine(84-120), sound: gunshot_or_explosion(120-144)</t>
@@ -663,22 +666,22 @@
         <v>11</v>
       </c>
       <c r="B5">
+        <v>0.8</v>
+      </c>
+      <c r="C5">
+        <v>0.8</v>
+      </c>
+      <c r="D5">
+        <v>0.8</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
         <v>1</v>
       </c>
-      <c r="C5">
-        <v>0.4</v>
-      </c>
-      <c r="D5">
-        <v>0.571</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H5">
         <v>5</v>
@@ -831,7 +834,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -885,6 +888,23 @@
         <v>30</v>
       </c>
     </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" t="s">
+        <v>31</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -926,7 +946,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -943,7 +963,7 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -987,7 +1007,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1004,7 +1024,7 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1021,7 +1041,7 @@
         <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1065,7 +1085,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1103,21 +1123,285 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>19</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>20</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>22</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
         <v>27</v>
       </c>
       <c r="D2" t="s">
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1141,10 +1425,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>19</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
       </c>
       <c r="C2" t="s">
         <v>18</v>
@@ -1153,42 +1437,42 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>20</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
       </c>
       <c r="C2" t="s">
         <v>18</v>
@@ -1197,271 +1481,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>21</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>22</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>23</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>29</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>30</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1478,7 +1498,7 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1522,7 +1542,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1539,7 +1559,7 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1583,7 +1603,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1627,7 +1647,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1644,7 +1664,7 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1688,7 +1708,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1705,7 +1725,7 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1749,7 +1769,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1787,13 +1807,13 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>47</v>
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1898,7 +1918,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1942,7 +1962,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
